--- a/pensum/ma04/MA04_Markedsundersokelser_Regneark_Markedsundersokelser.xlsx
+++ b/pensum/ma04/MA04_Markedsundersokelser_Regneark_Markedsundersokelser.xlsx
@@ -993,7 +993,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1124,6 +1124,10 @@
     </xf>
     <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1503,7 +1507,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="32.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
         <v>18</v>
       </c>
@@ -1515,7 +1519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="24.75" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
@@ -1846,8 +1850,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
+    <row ht="27" customHeight="true" r="41" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="33" r="A41" t="s">
         <v>82</v>
       </c>
       <c r="B41" s="20" t="s">
@@ -1857,8 +1861,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="s">
+    <row ht="27" customHeight="true" r="42" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="33" r="A42" t="s">
         <v>84</v>
       </c>
       <c r="B42" s="20" t="s">
@@ -2636,14 +2640,14 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
         <v>173</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c s="33" r="C5" t="s">
         <v>175</v>
       </c>
       <c r="D5" s="18" t="s">
@@ -2832,8 +2836,8 @@
         <v>OK — intervallene overlapper, så de to undersøkelsene motsier ikke hverandre</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
+    <row ht="27" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="33" r="A24" t="s">
         <v>194</v>
       </c>
       <c r="B24" s="30" t="str">
